--- a/leave_request_forms/037_religious_observation_time_off_form--leave_request_forms.xlsx
+++ b/leave_request_forms/037_religious_observation_time_off_form--leave_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yom_kippur',_'value':_1}</t>
+          <t>yom_kippur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yom Kippur', 'value': 1}</t>
+          <t>Yom Kippur</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rosh_hashanah',_'value':_2}</t>
+          <t>rosh_hashanah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rosh Hashanah', 'value': 2}</t>
+          <t>Rosh Hashanah</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'passover',_'value':_3}</t>
+          <t>passover</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Passover', 'value': 3}</t>
+          <t>Passover</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_"tisha_b'av",_'value':_4}</t>
+          <t>tisha_b'av</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': "Tisha B'Av", 'value': 4}</t>
+          <t>Tisha B'Av</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'sukkot',_'value':_5}</t>
+          <t>sukkot</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Sukkot', 'value': 5}</t>
+          <t>Sukkot</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'shavuot',_'value':_6}</t>
+          <t>shavuot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Shavuot', 'value': 6}</t>
+          <t>Shavuot</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'hanukkah',_'value':_7}</t>
+          <t>hanukkah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Hanukkah', 'value': 7}</t>
+          <t>Hanukkah</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'other',_'value':_8}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Other', 'value': 8}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chatjimmy',_'value':_1}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'chatjimmy', 'value': 1}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -916,148 +916,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chatjimmy',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'chatjimmy', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_id_choices</t>
+          <t>submitter_id_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chatjimmy',_'value':_3}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'chatjimmy', 'value': 3}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_id_choices</t>
+          <t>submitter_id_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'chatjimmy',_'value':_4}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'chatjimmy', 'value': 4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>assigned_tool_id_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'chatjimmy',_'value':_5}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'chatjimmy', 'value': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>submitter_id_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'chatjimmy',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'chatjimmy', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>submitter_id_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'chatjimmy',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'chatjimmy', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>submitter_id_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'chatjimmy',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'chatjimmy', 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>submitter_id_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'chatjimmy',_'value':_4}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'chatjimmy', 'value': 4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>submitter_id_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'chatjimmy',_'value':_5}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'chatjimmy', 'value': 5}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
